--- a/artfynd/A 26702-2026 artfynd.xlsx
+++ b/artfynd/A 26702-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308414</v>
+        <v>118308411</v>
       </c>
       <c r="B2" t="n">
-        <v>78227</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308416</v>
+        <v>118308415</v>
       </c>
       <c r="B3" t="n">
-        <v>78228</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,12 +872,7 @@
         <v>118308417</v>
       </c>
       <c r="B4" t="n">
-        <v>80448</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118308419</v>
+        <v>118308410</v>
       </c>
       <c r="B5" t="n">
-        <v>77423</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R5" t="n">
-        <v>6991727</v>
+        <v>6991747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118308411</v>
+        <v>118308409</v>
       </c>
       <c r="B6" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506715</v>
+        <v>506659</v>
       </c>
       <c r="R6" t="n">
-        <v>6991747</v>
+        <v>6991714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118308409</v>
+        <v>118308418</v>
       </c>
       <c r="B7" t="n">
-        <v>91786</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506659</v>
+        <v>506743</v>
       </c>
       <c r="R7" t="n">
-        <v>6991714</v>
+        <v>6991718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118308415</v>
+        <v>118308414</v>
       </c>
       <c r="B8" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118308413</v>
+        <v>118308412</v>
       </c>
       <c r="B9" t="n">
-        <v>79080</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118308410</v>
+        <v>118308419</v>
       </c>
       <c r="B10" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R10" t="n">
-        <v>6991747</v>
+        <v>6991727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118308412</v>
+        <v>118308416</v>
       </c>
       <c r="B11" t="n">
-        <v>79109</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118308418</v>
+        <v>118308413</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506743</v>
+        <v>506715</v>
       </c>
       <c r="R12" t="n">
-        <v>6991718</v>
+        <v>6991747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 26702-2026 artfynd.xlsx
+++ b/artfynd/A 26702-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308411</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308409</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308414</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308412</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308419</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308416</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>